--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/tester-design-medium.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/tester-design-medium.xlsx
@@ -466,10 +466,10 @@
         <v>8, 12, 16 ký tự — kiểm tra giá trị tối thiểu, trung bình và tối đa</v>
       </c>
       <c r="H2" t="str">
+        <v>7, 8, 16, 17 ký tự — kiểm tra các giá trị ngay trên biên và ngay dưới biên</v>
+      </c>
+      <c r="I2" t="str">
         <v>0, 8, 16, 100 ký tự — kiểm tra các giá trị cực trị ngẫu nhiên rộng</v>
-      </c>
-      <c r="I2" t="str">
-        <v>7, 8, 16, 17 ký tự — kiểm tra các giá trị ngay trên biên và ngay dưới biên</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -492,19 +492,19 @@
         <v>QA bắt buộc phải re-test trên bản build mới để xác minh bug thực sự đã được sửa, sau đó cập nhật trạng thái lỗi (Closed hoặc Reopen) tương ứng.</v>
       </c>
       <c r="F3" t="str">
-        <v>Chạy lại đúng các bước trong Bug Report trên bản build mới; nếu lỗi không còn thì đóng bug (Closed), nếu lỗi vẫn còn thì mở lại (Reopened)</v>
+        <v>Chạy lại toàn bộ kịch bản kiểm thử hiệu năng của hệ thống để xác thực tốc độ xử lý</v>
       </c>
       <c r="G3" t="str">
         <v>Đóng ngay lỗi đó trên hệ thống vì dev đã xác nhận sửa xong trong code</v>
       </c>
       <c r="H3" t="str">
+        <v>Chạy lại đúng các bước trong Bug Report trên bản build mới; nếu lỗi không còn thì đóng bug (Closed), nếu lỗi vẫn còn thì mở lại (Reopened)</v>
+      </c>
+      <c r="I3" t="str">
         <v>Viết một test case hoàn toàn mới để kiểm tra một tính năng khác của hệ thống</v>
       </c>
-      <c r="I3" t="str">
-        <v>Chạy lại toàn bộ kịch bản kiểm thử hiệu năng của hệ thống để xác thực tốc độ xử lý</v>
-      </c>
       <c r="J3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -530,10 +530,10 @@
         <v>Khi cần kiểm thử hiệu năng tải trang web dưới tác động của hàng ngàn request cùng lúc</v>
       </c>
       <c r="H4" t="str">
+        <v>Khi cần thiết kế các kịch bản kiểm thử tự động cho luồng thanh toán API</v>
+      </c>
+      <c r="I4" t="str">
         <v>Khi cần kiểm tra khả năng tương thích của ứng dụng trên nhiều phiên bản hệ điều hành Android</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Khi cần thiết kế các kịch bản kiểm thử tự động cho luồng thanh toán API</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -559,13 +559,13 @@
         <v>Sanity test là kiểm tra nhanh, tập trung hẹp vào một chức năng vừa được sửa đổi; Regression test là kiểm tra rộng, bao quát toàn bộ hệ thống để phát hiện lỗi hồi quy</v>
       </c>
       <c r="G5" t="str">
+        <v>Sanity test chỉ chạy được trên môi trường Production; Regression test chỉ chạy trên Local</v>
+      </c>
+      <c r="H5" t="str">
         <v>Sanity test do lập trình viên tự chạy; Regression test do kiểm thử viên chạy thủ công</v>
       </c>
-      <c r="H5" t="str">
+      <c r="I5" t="str">
         <v>Sanity test kiểm tra tính tương thích; Regression test kiểm tra tính hiệu năng hệ thống</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Sanity test chỉ chạy được trên môi trường Production; Regression test chỉ chạy trên Local</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -588,19 +588,19 @@
         <v>Lỗi crash tính năng chính (thanh toán) vi phạm nặng nề trải nghiệm người dùng và quy trình nghiệp vụ cốt lõi, do đó cần xếp vào Severity Critical và Priority High (sửa ngay lập tức).</v>
       </c>
       <c r="F6" t="str">
+        <v>Severity: Critical, Priority: Low — vì khách hàng có thể dùng chuyển khoản thủ công thay thế</v>
+      </c>
+      <c r="G6" t="str">
         <v>Severity: Critical (Nghiêm trọng), Priority: High (Ưu tiên cao) — lỗi chặn chức năng cốt lõi của dự án và làm hỏng trải nghiệm người dùng ngay lập tức</v>
       </c>
-      <c r="G6" t="str">
+      <c r="H6" t="str">
         <v>Severity: Low, Priority: High — vì giao diện nút thanh toán vẫn hiển thị rất đẹp mắt</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Severity: Critical, Priority: Low — vì khách hàng có thể dùng chuyển khoản thủ công thay thế</v>
       </c>
       <c r="I6" t="str">
         <v>Severity: Medium, Priority: Medium — lỗi ở mức trung bình vì ứng dụng vẫn mở lại được</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -620,19 +620,19 @@
         <v>Kiểm thử chuyển trạng thái giúp bao phủ đầy đủ các luồng chuyển dịch trạng thái hợp lệ và phát hiện các luồng chuyển dịch sai logic (ví dụ: Đơn hàng đã hủy không được phép chuyển sang Đang giao).</v>
       </c>
       <c r="F7" t="str">
+        <v>Hệ thống kho báo cáo tĩnh chỉ hiển thị dữ liệu thô dạng bảng của doanh nghiệp</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Hệ thống landing page giới thiệu sản phẩm chỉ chứa văn bản thô và hình ảnh quảng cáo</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Các ứng dụng tính toán công thức toán học độc lập không lưu trữ dữ liệu</v>
+      </c>
+      <c r="I7" t="str">
         <v>Hệ thống có các đối tượng thay đổi trạng thái tuần tự dựa trên các sự kiện kích hoạt cụ thể (ví dụ: Vòng đời đơn hàng từ Chờ duyệt -&gt; Đang giao -&gt; Thành công)</v>
       </c>
-      <c r="G7" t="str">
-        <v>Hệ thống kho báo cáo tĩnh chỉ hiển thị dữ liệu thô dạng bảng của doanh nghiệp</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Hệ thống landing page giới thiệu sản phẩm chỉ chứa văn bản thô và hình ảnh quảng cáo</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Các ứng dụng tính toán công thức toán học độc lập không lưu trữ dữ liệu</v>
-      </c>
       <c r="J7">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -684,19 +684,19 @@
         <v>Nguyên lý "Kiểm thử sớm" (Early Testing) giúp giảm thiểu chi phí sửa lỗi. Phát hiện lỗi logic trên tài liệu yêu cầu (SRS) rẻ hơn gấp hàng chục lần so với sửa lỗi sau khi dev đã code xong.</v>
       </c>
       <c r="F9" t="str">
+        <v>Bắt đầu sau khi khách hàng đã thực hiện xong kiểm thử chấp nhận UAT trên Production</v>
+      </c>
+      <c r="G9" t="str">
         <v>Bắt đầu ngay từ giai đoạn khơi gợi và phân tích yêu cầu (Early Testing) — review tài liệu yêu cầu cùng BA để phát hiện sớm các lỗi logic nghiệp vụ trước khi code</v>
       </c>
-      <c r="G9" t="str">
+      <c r="H9" t="str">
         <v>Bắt đầu khi lập trình viên đã hoàn thành 100% mã nguồn và bàn giao toàn bộ hệ thống sang QA</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Bắt đầu sau khi khách hàng đã thực hiện xong kiểm thử chấp nhận UAT trên Production</v>
       </c>
       <c r="I9" t="str">
         <v>Bắt đầu vào ngày cuối cùng của Sprint phát triển để kiểm tra nhanh giao diện ứng dụng</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -719,10 +719,10 @@
         <v>Để cung cấp tiêu chuẩn so sánh khách quan với kết quả thực tế khi chạy test, giúp xác định chính xác ca kiểm thử đó Pass hay Fail</v>
       </c>
       <c r="G10" t="str">
+        <v>Để tự động hóa việc tính toán thời gian phản hồi của máy chủ ứng dụng di động</v>
+      </c>
+      <c r="H10" t="str">
         <v>Để hướng dẫn lập trình viên cách viết các câu lệnh điều kiện rẽ nhánh trong code</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Để tự động hóa việc tính toán thời gian phản hồi của máy chủ ứng dụng di động</v>
       </c>
       <c r="I10" t="str">
         <v>Để hiển thị thông tin hướng dẫn sử dụng sản phẩm cho người dùng cuối</v>
@@ -748,19 +748,19 @@
         <v>Ad-hoc testing là quá trình test ngẫu hứng, tự do không theo khuôn mẫu để nhanh chóng tìm ra các lỗi nghiêm trọng mà test case thông thường bỏ sót.</v>
       </c>
       <c r="F11" t="str">
-        <v>Là kiểm thử ngẫu nhiên, không lập kế hoạch, không có tài liệu test case và diễn ra bất chợt để tìm bug nhanh</v>
+        <v>Là kiểm thử chỉ tập trung vào việc đọc cấu trúc cơ sở dữ liệu quan hệ SQL</v>
       </c>
       <c r="G11" t="str">
         <v>Là kiểm thử bắt buộc phải sử dụng các công cụ tự động hóa như Selenium hoặc JMeter</v>
       </c>
       <c r="H11" t="str">
-        <v>Là kiểm thử chỉ tập trung vào việc đọc cấu trúc cơ sở dữ liệu quan hệ SQL</v>
+        <v>Là kiểm thử ngẫu nhiên, không lập kế hoạch, không có tài liệu test case và diễn ra bất chợt để tìm bug nhanh</v>
       </c>
       <c r="I11" t="str">
         <v>Là kiểm thử do khách hàng thực hiện trên môi trường Production để nghiệm thu</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
